--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Hp</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>血量</t>
+          <t>当前生命值</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -521,12 +521,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Mp</t>
+          <t>Mana</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>蓝量</t>
+          <t>当前法力值</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -537,12 +537,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Spd</t>
+          <t>MoveSpeed</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>速度</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Atk</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t>Stamina</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>耐力</t>
+          <t>当前耐力值</t>
         </is>
       </c>
     </row>
@@ -597,12 +597,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HpMax</t>
+          <t>MaxHealth</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>血上限</t>
+          <t>生命上限</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MpMax</t>
+          <t>MaxMana</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>魔力上限</t>
+          <t>法力上限</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SpMax</t>
+          <t>MaxStamina</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -642,34 +642,74 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AtkRate</t>
+          <t>AttackSpeed</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>攻击加成百分比</t>
+          <t>攻击速度</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>命中率</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>闪避率</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CriticalChance</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CriticalMultiplier</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>暴击倍率</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
